--- a/healthcare_surveys/028_hiv_policy_feedback_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/028_hiv_policy_feedback_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'highly_effective'}</t>
+          <t>highly_effective</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Highly Effective'}</t>
+          <t>Highly Effective</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_effective'}</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Effective'}</t>
+          <t>Somewhat Effective</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_not_effective'}</t>
+          <t>somewhat_not_effective</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Not Effective'}</t>
+          <t>Somewhat Not Effective</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'not_effective'}</t>
+          <t>not_effective</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Not Effective'}</t>
+          <t>Not Effective</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'policy_clarity'}</t>
+          <t>policy_clarity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Policy clarity'}</t>
+          <t>Policy clarity</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'community_engagement'}</t>
+          <t>community_engagement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Community engagement'}</t>
+          <t>Community engagement</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'region_1'}</t>
+          <t>region_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Region 1'}</t>
+          <t>Region 1</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'region_2'}</t>
+          <t>region_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Region 2'}</t>
+          <t>Region 2</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'region_3'}</t>
+          <t>region_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Region 3'}</t>
+          <t>Region 3</t>
         </is>
       </c>
     </row>
